--- a/deliverables/canberra_str_model.xlsx
+++ b/deliverables/canberra_str_model.xlsx
@@ -11,6 +11,8 @@
     <sheet name="Inputs" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Management" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Leverage &amp; Tax" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -106,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,6 +151,11 @@
     <xf numFmtId="165" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -514,10 +521,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -563,7 +570,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Base STR NOI</t>
+          <t>Base STR NOI (managed)</t>
         </is>
       </c>
       <c r="B7" s="4">
@@ -574,115 +581,148 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Long-term rental NOI</t>
+          <t>Base STR NOI (self-managed)</t>
         </is>
       </c>
       <c r="B8" s="4">
-        <f>Scenarios!B22</f>
+        <f>Management!C7</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Base STR advantage vs LTR (pre-amort)</t>
+          <t>Long-term rental NOI</t>
         </is>
       </c>
       <c r="B9" s="4">
-        <f>Scenarios!D25</f>
+        <f>Scenarios!B21</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Base STR advantage vs LTR (managed)</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>Scenarios!D12-Scenarios!B21</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>Self-managing adds</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <f>Management!B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>Conservative STR NOI (p25)</t>
         </is>
       </c>
-      <c r="B11" s="4">
+      <c r="B13" s="4">
         <f>Scenarios!C12</f>
         <v/>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Aggressive STR NOI (p75)</t>
-        </is>
-      </c>
-      <c r="B12" s="4">
-        <f>Scenarios!E12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>STR base net yield</t>
-        </is>
-      </c>
-      <c r="B14" s="5">
-        <f>Scenarios!D12/Inputs!B5</f>
+          <t>Aggressive STR NOI (p75)</t>
+        </is>
+      </c>
+      <c r="B14" s="4">
+        <f>Scenarios!E12</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>LTR net yield</t>
-        </is>
-      </c>
-      <c r="B15" s="5">
-        <f>Scenarios!B22/Inputs!B5</f>
-        <v/>
-      </c>
+      <c r="A15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Break-even occupancy to match LTR (base ADR)</t>
-        </is>
-      </c>
-      <c r="B16" s="6">
-        <f>Scenarios!B26/(Inputs!C10*365)</f>
+          <t>STR base net yield</t>
+        </is>
+      </c>
+      <c r="B16" s="5">
+        <f>Scenarios!D12/Inputs!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>LTR net yield</t>
+        </is>
+      </c>
+      <c r="B17" s="5">
+        <f>Scenarios!B21/Inputs!B5</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Break-even occupancy to match LTR</t>
+        </is>
+      </c>
+      <c r="B18" s="6">
+        <f>Scenarios!B25/(Inputs!C10*365)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Total return on equity (all-cash, STR)</t>
+        </is>
+      </c>
+      <c r="B19" s="5">
+        <f>'Leverage &amp; Tax'!B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>At median execution, STR is roughly line-ball with a $750/wk long-term rent, for much more work and risk. STR wins clearly only if run top-quartile (p75). Both yields are low because it is a $1M house — a capital-growth, low-yield market.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
+      <c r="B21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Managed, short-term is line-ball with a $750/wk long-term rent; SELF-MANAGED it clears it by ~$9-10k/yr. Add capital growth + leverage and the two nearly converge on total return — because growth (common to both) dominates. Decision hinges on: do you self-manage, and is the operating work worth the modest income edge. Both are low-yield on a $1M asset.</t>
+        </is>
+      </c>
+    </row>
     <row r="23"/>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Source: AirROI API (pulled 2026-08-08). Edit blue cells in Inputs; all else recalculates.</t>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Source: AirROI API (8 Aug 2026). Edit blue cells in Inputs; all results recalculate. Tax indicative — confirm with an accountant.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A19:B23"/>
+    <mergeCell ref="A22:B26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -694,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1001,108 +1041,164 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Has mortgage? (1=yes, 0=no)</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Leverage, tax &amp; growth</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Loan balance</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="n">
-        <v>0</v>
+          <t>Mortgage interest rate</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>edit to your rate</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Interest rate</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="n">
-        <v>0.062</v>
+          <t>Marginal tax rate (incl Medicare)</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>37%+2% assumed</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Long-term rental baseline</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>STR depreciation (annual)</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>new $30k fit-out</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Weekly rent</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="n">
-        <v>750</v>
+          <t>LTR depreciation (annual)</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>2000</v>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>USER-PROVIDED</t>
+          <t>minimal, older home</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Vacancy (weeks/year)</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="n">
-        <v>2</v>
+          <t>Capital growth rate (p.a.)</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>common to STR &amp; LTR</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Management fee (%)</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Long-term rental baseline</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Maintenance (annual)</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="n">
-        <v>1500</v>
+          <t>Weekly rent</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>USER-PROVIDED</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Council rates (annual)</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="n">
-        <v>3800</v>
+          <t>Vacancy (weeks/year)</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
+          <t>Management fee (%)</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance (annual)</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Council rates (annual)</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
           <t>Insurance (annual)</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n">
+      <c r="B39" s="14" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1117,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1347,162 +1443,143 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  less mortgage interest</t>
-        </is>
-      </c>
-      <c r="C14" s="20">
-        <f>-Inputs!B27*Inputs!B28*Inputs!B29</f>
-        <v/>
-      </c>
-      <c r="D14" s="20">
-        <f>-Inputs!B27*Inputs!B28*Inputs!B29</f>
-        <v/>
-      </c>
-      <c r="E14" s="20">
-        <f>-Inputs!B27*Inputs!B28*Inputs!B29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>Net cash flow</t>
-        </is>
-      </c>
-      <c r="C15" s="4">
-        <f>C12+C13+C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="4">
-        <f>D12+D13+D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="4">
-        <f>E12+E13+E14</f>
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>Net cash flow (all-cash)</t>
+        </is>
+      </c>
+      <c r="C14" s="4">
+        <f>C12+C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="4">
+        <f>D12+D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="4">
+        <f>E12+E13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Gross yield (rev / value)</t>
+        </is>
+      </c>
+      <c r="C16" s="27">
+        <f>C7/Inputs!B5</f>
+        <v/>
+      </c>
+      <c r="D16" s="27">
+        <f>D7/Inputs!B5</f>
+        <v/>
+      </c>
+      <c r="E16" s="27">
+        <f>E7/Inputs!B5</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Gross yield (rev / value)</t>
-        </is>
-      </c>
-      <c r="C17" s="27">
-        <f>C7/Inputs!B5</f>
-        <v/>
-      </c>
-      <c r="D17" s="27">
-        <f>D7/Inputs!B5</f>
-        <v/>
-      </c>
-      <c r="E17" s="27">
-        <f>E7/Inputs!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>Net yield (NOI / value)</t>
         </is>
       </c>
-      <c r="C18" s="5">
+      <c r="C17" s="5">
         <f>C12/Inputs!B5</f>
         <v/>
       </c>
-      <c r="D18" s="5">
+      <c r="D17" s="5">
         <f>D12/Inputs!B5</f>
         <v/>
       </c>
-      <c r="E18" s="5">
+      <c r="E17" s="5">
         <f>E12/Inputs!B5</f>
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Long-term rental baseline</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+    </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Long-term rental baseline</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>LTR gross income</t>
+        </is>
+      </c>
+      <c r="B20" s="28">
+        <f>Inputs!B34*(52-Inputs!B35)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>LTR gross income</t>
-        </is>
-      </c>
-      <c r="B21" s="28">
-        <f>Inputs!B31*(52-Inputs!B32)</f>
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>LTR NOI</t>
+        </is>
+      </c>
+      <c r="B21" s="4">
+        <f>B20-B20*Inputs!B36-Inputs!B37-Inputs!B38-Inputs!B39</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
-        <is>
-          <t>LTR NOI</t>
-        </is>
-      </c>
-      <c r="B22" s="4">
-        <f>B21-B21*Inputs!B33-Inputs!B34-Inputs!B35-Inputs!B36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>LTR net yield</t>
         </is>
       </c>
-      <c r="B23" s="29">
-        <f>B22/Inputs!B5</f>
+      <c r="B22" s="29">
+        <f>B21/Inputs!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>STR NOI − LTR NOI</t>
+        </is>
+      </c>
+      <c r="C24" s="4">
+        <f>C12-$B$21</f>
+        <v/>
+      </c>
+      <c r="D24" s="4">
+        <f>D12-$B$21</f>
+        <v/>
+      </c>
+      <c r="E24" s="4">
+        <f>E12-$B$21</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>STR NOI − LTR NOI</t>
-        </is>
-      </c>
-      <c r="C25" s="4">
-        <f>C12-$B$22</f>
-        <v/>
-      </c>
-      <c r="D25" s="4">
-        <f>D12-$B$22</f>
-        <v/>
-      </c>
-      <c r="E25" s="4">
-        <f>E12-$B$22</f>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Break-even gross rev to match LTR</t>
+        </is>
+      </c>
+      <c r="B25" s="28">
+        <f>(B21+(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23))/(1-Inputs!B13-Inputs!B17-Inputs!B16)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Break-even gross rev to match LTR</t>
-        </is>
-      </c>
-      <c r="B26" s="28">
-        <f>(B22+(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23))/(1-Inputs!B13-Inputs!B17-Inputs!B16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">  → implied occupancy at Base ADR</t>
         </is>
       </c>
-      <c r="B27" s="30">
-        <f>B26/(Inputs!C10*365)</f>
+      <c r="B26" s="30">
+        <f>B25/(Inputs!C10*365)</f>
         <v/>
       </c>
     </row>
@@ -1749,8 +1826,675 @@
         </is>
       </c>
       <c r="B12" s="29">
-        <f>Scenarios!B22/Inputs!B5</f>
-        <v/>
+        <f>Scenarios!B21/Inputs!B5</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Self-managed vs Professionally managed (base case)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Base case — per year</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>Managed</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Self-managed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Gross revenue</t>
+        </is>
+      </c>
+      <c r="B4" s="28">
+        <f>Scenarios!D7</f>
+        <v/>
+      </c>
+      <c r="C4" s="28">
+        <f>Scenarios!D7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Management fee</t>
+        </is>
+      </c>
+      <c r="B5" s="28">
+        <f>-Scenarios!D7*Inputs!B16</f>
+        <v/>
+      </c>
+      <c r="C5" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Other costs (levy+platform+fixed)</t>
+        </is>
+      </c>
+      <c r="B6" s="28">
+        <f>-Scenarios!D7*(Inputs!B13+Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)</f>
+        <v/>
+      </c>
+      <c r="C6" s="28">
+        <f>-Scenarios!D7*(Inputs!B13+Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>Net operating income</t>
+        </is>
+      </c>
+      <c r="B7" s="25">
+        <f>B4+B5+B6</f>
+        <v/>
+      </c>
+      <c r="C7" s="25">
+        <f>C4+C5+C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Net yield</t>
+        </is>
+      </c>
+      <c r="B8" s="29">
+        <f>B7/Inputs!B5</f>
+        <v/>
+      </c>
+      <c r="C8" s="29">
+        <f>C7/Inputs!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>vs long-term rent NOI</t>
+        </is>
+      </c>
+      <c r="B9" s="28">
+        <f>B7-Scenarios!B21</f>
+        <v/>
+      </c>
+      <c r="C9" s="28">
+        <f>C7-Scenarios!B21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>Self-managing adds (per year)</t>
+        </is>
+      </c>
+      <c r="B11" s="32">
+        <f>C7-B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Note: self-managing saves the fee but is your unpaid time (guest comms, cleaning coordination, pricing).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Leverage, Tax &amp; Total Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Base STR (managed) vs long-term rent, by loan-to-value. Capital growth is common to both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Base STR (managed)</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>Per year (AUD)</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>All-cash</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>60% LVR</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>80% LVR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>LVR</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Loan</t>
+        </is>
+      </c>
+      <c r="B7" s="28">
+        <f>Inputs!B5*B6</f>
+        <v/>
+      </c>
+      <c r="C7" s="28">
+        <f>Inputs!B5*C6</f>
+        <v/>
+      </c>
+      <c r="D7" s="28">
+        <f>Inputs!B5*D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Your equity</t>
+        </is>
+      </c>
+      <c r="B8" s="28">
+        <f>Inputs!B5*(1-B6)+Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="C8" s="28">
+        <f>Inputs!B5*(1-C6)+Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="D8" s="28">
+        <f>Inputs!B5*(1-D6)+Inputs!B25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Interest cost</t>
+        </is>
+      </c>
+      <c r="B9" s="28">
+        <f>-B7*Inputs!B28</f>
+        <v/>
+      </c>
+      <c r="C9" s="28">
+        <f>-C7*Inputs!B28</f>
+        <v/>
+      </c>
+      <c r="D9" s="28">
+        <f>-D7*Inputs!B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Pre-tax cash flow</t>
+        </is>
+      </c>
+      <c r="B10" s="28">
+        <f>Scenarios!D12+B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="28">
+        <f>Scenarios!D12+C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="28">
+        <f>Scenarios!D12+D9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Taxable income</t>
+        </is>
+      </c>
+      <c r="B11" s="28">
+        <f>Scenarios!D12+B9-Inputs!B30</f>
+        <v/>
+      </c>
+      <c r="C11" s="28">
+        <f>Scenarios!D12+C9-Inputs!B30</f>
+        <v/>
+      </c>
+      <c r="D11" s="28">
+        <f>Scenarios!D12+D9-Inputs!B30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Tax / (refund)</t>
+        </is>
+      </c>
+      <c r="B12" s="28">
+        <f>-B11*Inputs!B29</f>
+        <v/>
+      </c>
+      <c r="C12" s="28">
+        <f>-C11*Inputs!B29</f>
+        <v/>
+      </c>
+      <c r="D12" s="28">
+        <f>-D11*Inputs!B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>After-tax cash flow</t>
+        </is>
+      </c>
+      <c r="B13" s="28">
+        <f>B10+B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="28">
+        <f>C10+C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="28">
+        <f>D10+D12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Cash-on-cash (after tax)</t>
+        </is>
+      </c>
+      <c r="B14" s="29">
+        <f>B13/B8</f>
+        <v/>
+      </c>
+      <c r="C14" s="29">
+        <f>C13/C8</f>
+        <v/>
+      </c>
+      <c r="D14" s="29">
+        <f>D13/D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Capital gain</t>
+        </is>
+      </c>
+      <c r="B15" s="28">
+        <f>Inputs!B5*Inputs!B32</f>
+        <v/>
+      </c>
+      <c r="C15" s="28">
+        <f>Inputs!B5*Inputs!B32</f>
+        <v/>
+      </c>
+      <c r="D15" s="28">
+        <f>Inputs!B5*Inputs!B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Total return on equity</t>
+        </is>
+      </c>
+      <c r="B16" s="34">
+        <f>(B13+B15)/B8</f>
+        <v/>
+      </c>
+      <c r="C16" s="34">
+        <f>(C13+C15)/C8</f>
+        <v/>
+      </c>
+      <c r="D16" s="34">
+        <f>(D13+D15)/D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Long-term rental</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>Per year (AUD)</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>All-cash</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>60% LVR</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>80% LVR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>LVR</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Loan</t>
+        </is>
+      </c>
+      <c r="B22" s="28">
+        <f>Inputs!B5*B21</f>
+        <v/>
+      </c>
+      <c r="C22" s="28">
+        <f>Inputs!B5*C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="28">
+        <f>Inputs!B5*D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Your equity</t>
+        </is>
+      </c>
+      <c r="B23" s="28">
+        <f>Inputs!B5*(1-B21)+0</f>
+        <v/>
+      </c>
+      <c r="C23" s="28">
+        <f>Inputs!B5*(1-C21)+0</f>
+        <v/>
+      </c>
+      <c r="D23" s="28">
+        <f>Inputs!B5*(1-D21)+0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Interest cost</t>
+        </is>
+      </c>
+      <c r="B24" s="28">
+        <f>-B22*Inputs!B28</f>
+        <v/>
+      </c>
+      <c r="C24" s="28">
+        <f>-C22*Inputs!B28</f>
+        <v/>
+      </c>
+      <c r="D24" s="28">
+        <f>-D22*Inputs!B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Pre-tax cash flow</t>
+        </is>
+      </c>
+      <c r="B25" s="28">
+        <f>Scenarios!B21+B24</f>
+        <v/>
+      </c>
+      <c r="C25" s="28">
+        <f>Scenarios!B21+C24</f>
+        <v/>
+      </c>
+      <c r="D25" s="28">
+        <f>Scenarios!B21+D24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Taxable income</t>
+        </is>
+      </c>
+      <c r="B26" s="28">
+        <f>Scenarios!B21+B24-Inputs!B31</f>
+        <v/>
+      </c>
+      <c r="C26" s="28">
+        <f>Scenarios!B21+C24-Inputs!B31</f>
+        <v/>
+      </c>
+      <c r="D26" s="28">
+        <f>Scenarios!B21+D24-Inputs!B31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Tax / (refund)</t>
+        </is>
+      </c>
+      <c r="B27" s="28">
+        <f>-B26*Inputs!B29</f>
+        <v/>
+      </c>
+      <c r="C27" s="28">
+        <f>-C26*Inputs!B29</f>
+        <v/>
+      </c>
+      <c r="D27" s="28">
+        <f>-D26*Inputs!B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>After-tax cash flow</t>
+        </is>
+      </c>
+      <c r="B28" s="28">
+        <f>B25+B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="28">
+        <f>C25+C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="28">
+        <f>D25+D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Cash-on-cash (after tax)</t>
+        </is>
+      </c>
+      <c r="B29" s="29">
+        <f>B28/B23</f>
+        <v/>
+      </c>
+      <c r="C29" s="29">
+        <f>C28/C23</f>
+        <v/>
+      </c>
+      <c r="D29" s="29">
+        <f>D28/D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Capital gain</t>
+        </is>
+      </c>
+      <c r="B30" s="28">
+        <f>Inputs!B5*Inputs!B32</f>
+        <v/>
+      </c>
+      <c r="C30" s="28">
+        <f>Inputs!B5*Inputs!B32</f>
+        <v/>
+      </c>
+      <c r="D30" s="28">
+        <f>Inputs!B5*Inputs!B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Total return on equity</t>
+        </is>
+      </c>
+      <c r="B31" s="34">
+        <f>(B28+B30)/B23</f>
+        <v/>
+      </c>
+      <c r="C31" s="34">
+        <f>(C28+C30)/C23</f>
+        <v/>
+      </c>
+      <c r="D31" s="34">
+        <f>(D28+D30)/D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Negative cash-on-cash under leverage = negative gearing (loss offsets other income at your marginal rate). Total return rises with leverage because it amplifies capital growth on a smaller equity base. Indicative only — not tax advice.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/deliverables/canberra_str_model.xlsx
+++ b/deliverables/canberra_str_model.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Management" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Leverage &amp; Tax" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="10-Year Projection" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -694,27 +695,39 @@
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>10-yr wealth: self-managed STR vs LTR</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>'10-Year Projection'!I16</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="B22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Managed, short-term is line-ball with a $750/wk long-term rent; SELF-MANAGED it clears it by ~$9-10k/yr. Add capital growth + leverage and the two nearly converge on total return — because growth (common to both) dominates. Decision hinges on: do you self-manage, and is the operating work worth the modest income edge. Both are low-yield on a $1M asset.</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24"/>
     <row r="25"/>
     <row r="26"/>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="27"/>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Source: AirROI API (8 Aug 2026). Edit blue cells in Inputs; all results recalculate. Tax indicative — confirm with an accountant.</t>
         </is>
@@ -722,7 +735,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A22:B26"/>
+    <mergeCell ref="A23:B27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -734,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1127,78 +1140,98 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Long-term rental baseline</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Income growth (rent/rev, p.a.)</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Weekly rent</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="n">
-        <v>750</v>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>USER-PROVIDED</t>
-        </is>
+          <t>Cost inflation (p.a.)</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Vacancy (weeks/year)</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="n">
-        <v>2</v>
-      </c>
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Long-term rental baseline</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Management fee (%)</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="n">
-        <v>0.07000000000000001</v>
+          <t>Weekly rent</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>USER-PROVIDED</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Maintenance (annual)</t>
-        </is>
-      </c>
-      <c r="B37" s="14" t="n">
-        <v>1500</v>
+          <t>Vacancy (weeks/year)</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Council rates (annual)</t>
-        </is>
-      </c>
-      <c r="B38" s="14" t="n">
-        <v>3800</v>
+          <t>Management fee (%)</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
+          <t>Maintenance (annual)</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Council rates (annual)</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
           <t>Insurance (annual)</t>
         </is>
       </c>
-      <c r="B39" s="14" t="n">
+      <c r="B41" s="14" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1516,7 +1549,7 @@
         </is>
       </c>
       <c r="B20" s="28">
-        <f>Inputs!B34*(52-Inputs!B35)</f>
+        <f>Inputs!B36*(52-Inputs!B37)</f>
         <v/>
       </c>
     </row>
@@ -1527,7 +1560,7 @@
         </is>
       </c>
       <c r="B21" s="4">
-        <f>B20-B20*Inputs!B36-Inputs!B37-Inputs!B38-Inputs!B39</f>
+        <f>B20-B20*Inputs!B38-Inputs!B39-Inputs!B40-Inputs!B41</f>
         <v/>
       </c>
     </row>
@@ -2500,4 +2533,585 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>10-Year Wealth Projection (all-cash, after-tax)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Rent/revenue grow at income growth; costs at cost inflation; levy steps to 7.5% in 2027; capital growth on value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>STR self cash</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>STR self cum</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>STR mgd cash</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>STR mgd cum</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>LTR cash</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>LTR cum</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Property value</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>Wealth: self</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
+        <is>
+          <t>Wealth: mgd</t>
+        </is>
+      </c>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>Wealth: LTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(1-1)*(1-IF(2026&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(1-1))-((Scenarios!D7*(1+Inputs!B33)^(1-1)*(1-IF(2026&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(1-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="C5" s="28">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="D5" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(1-1)*(1-IF(2026&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(1-1))-((Scenarios!D7*(1+Inputs!B33)^(1-1)*(1-IF(2026&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(1-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="E5" s="28">
+        <f>D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="28">
+        <f>((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(1-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(1-1))-((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(1-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(1-1))-Inputs!B31)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="G5" s="28">
+        <f>F5</f>
+        <v/>
+      </c>
+      <c r="H5" s="28">
+        <f>Inputs!B5*(1+Inputs!B32)^1</f>
+        <v/>
+      </c>
+      <c r="I5" s="28">
+        <f>H5+C5-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="J5" s="28">
+        <f>H5+E5-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="K5" s="28">
+        <f>H5+G5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B6" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(2-1)*(1-IF(2027&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(2-1))-((Scenarios!D7*(1+Inputs!B33)^(2-1)*(1-IF(2027&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(2-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="C6" s="28">
+        <f>C5+B6</f>
+        <v/>
+      </c>
+      <c r="D6" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(2-1)*(1-IF(2027&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(2-1))-((Scenarios!D7*(1+Inputs!B33)^(2-1)*(1-IF(2027&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(2-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="E6" s="28">
+        <f>E5+D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="28">
+        <f>((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(2-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(2-1))-((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(2-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(2-1))-Inputs!B31)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="G6" s="28">
+        <f>G5+F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="28">
+        <f>Inputs!B5*(1+Inputs!B32)^2</f>
+        <v/>
+      </c>
+      <c r="I6" s="28">
+        <f>H6+C6-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="J6" s="28">
+        <f>H6+E6-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="K6" s="28">
+        <f>H6+G6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B7" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(3-1)*(1-IF(2028&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(3-1))-((Scenarios!D7*(1+Inputs!B33)^(3-1)*(1-IF(2028&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(3-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="C7" s="28">
+        <f>C6+B7</f>
+        <v/>
+      </c>
+      <c r="D7" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(3-1)*(1-IF(2028&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(3-1))-((Scenarios!D7*(1+Inputs!B33)^(3-1)*(1-IF(2028&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(3-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>E6+D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="28">
+        <f>((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(3-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(3-1))-((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(3-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(3-1))-Inputs!B31)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="G7" s="28">
+        <f>G6+F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="28">
+        <f>Inputs!B5*(1+Inputs!B32)^3</f>
+        <v/>
+      </c>
+      <c r="I7" s="28">
+        <f>H7+C7-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="J7" s="28">
+        <f>H7+E7-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="K7" s="28">
+        <f>H7+G7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B8" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(4-1)*(1-IF(2029&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(4-1))-((Scenarios!D7*(1+Inputs!B33)^(4-1)*(1-IF(2029&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(4-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="C8" s="28">
+        <f>C7+B8</f>
+        <v/>
+      </c>
+      <c r="D8" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(4-1)*(1-IF(2029&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(4-1))-((Scenarios!D7*(1+Inputs!B33)^(4-1)*(1-IF(2029&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(4-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="E8" s="28">
+        <f>E7+D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="28">
+        <f>((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(4-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(4-1))-((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(4-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(4-1))-Inputs!B31)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="G8" s="28">
+        <f>G7+F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="28">
+        <f>Inputs!B5*(1+Inputs!B32)^4</f>
+        <v/>
+      </c>
+      <c r="I8" s="28">
+        <f>H8+C8-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="J8" s="28">
+        <f>H8+E8-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="K8" s="28">
+        <f>H8+G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B9" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(5-1)*(1-IF(2030&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(5-1))-((Scenarios!D7*(1+Inputs!B33)^(5-1)*(1-IF(2030&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(5-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="C9" s="28">
+        <f>C8+B9</f>
+        <v/>
+      </c>
+      <c r="D9" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(5-1)*(1-IF(2030&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(5-1))-((Scenarios!D7*(1+Inputs!B33)^(5-1)*(1-IF(2030&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(5-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="E9" s="28">
+        <f>E8+D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="28">
+        <f>((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(5-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(5-1))-((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(5-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(5-1))-Inputs!B31)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="G9" s="28">
+        <f>G8+F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="28">
+        <f>Inputs!B5*(1+Inputs!B32)^5</f>
+        <v/>
+      </c>
+      <c r="I9" s="28">
+        <f>H9+C9-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="J9" s="28">
+        <f>H9+E9-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="K9" s="28">
+        <f>H9+G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B10" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(6-1)*(1-IF(2031&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(6-1))-((Scenarios!D7*(1+Inputs!B33)^(6-1)*(1-IF(2031&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(6-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="C10" s="28">
+        <f>C9+B10</f>
+        <v/>
+      </c>
+      <c r="D10" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(6-1)*(1-IF(2031&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(6-1))-((Scenarios!D7*(1+Inputs!B33)^(6-1)*(1-IF(2031&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(6-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="E10" s="28">
+        <f>E9+D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="28">
+        <f>((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(6-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(6-1))-((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(6-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(6-1))-Inputs!B31)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="G10" s="28">
+        <f>G9+F10</f>
+        <v/>
+      </c>
+      <c r="H10" s="28">
+        <f>Inputs!B5*(1+Inputs!B32)^6</f>
+        <v/>
+      </c>
+      <c r="I10" s="28">
+        <f>H10+C10-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="J10" s="28">
+        <f>H10+E10-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="K10" s="28">
+        <f>H10+G10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B11" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(7-1)*(1-IF(2032&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(7-1))-((Scenarios!D7*(1+Inputs!B33)^(7-1)*(1-IF(2032&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(7-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="C11" s="28">
+        <f>C10+B11</f>
+        <v/>
+      </c>
+      <c r="D11" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(7-1)*(1-IF(2032&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(7-1))-((Scenarios!D7*(1+Inputs!B33)^(7-1)*(1-IF(2032&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(7-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="E11" s="28">
+        <f>E10+D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="28">
+        <f>((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(7-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(7-1))-((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(7-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(7-1))-Inputs!B31)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="G11" s="28">
+        <f>G10+F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="28">
+        <f>Inputs!B5*(1+Inputs!B32)^7</f>
+        <v/>
+      </c>
+      <c r="I11" s="28">
+        <f>H11+C11-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="J11" s="28">
+        <f>H11+E11-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="K11" s="28">
+        <f>H11+G11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B12" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(8-1)*(1-IF(2033&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(8-1))-((Scenarios!D7*(1+Inputs!B33)^(8-1)*(1-IF(2033&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(8-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="C12" s="28">
+        <f>C11+B12</f>
+        <v/>
+      </c>
+      <c r="D12" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(8-1)*(1-IF(2033&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(8-1))-((Scenarios!D7*(1+Inputs!B33)^(8-1)*(1-IF(2033&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(8-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="E12" s="28">
+        <f>E11+D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="28">
+        <f>((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(8-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(8-1))-((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(8-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(8-1))-Inputs!B31)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="G12" s="28">
+        <f>G11+F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="28">
+        <f>Inputs!B5*(1+Inputs!B32)^8</f>
+        <v/>
+      </c>
+      <c r="I12" s="28">
+        <f>H12+C12-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="J12" s="28">
+        <f>H12+E12-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="K12" s="28">
+        <f>H12+G12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B13" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(9-1)*(1-IF(2034&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(9-1))-((Scenarios!D7*(1+Inputs!B33)^(9-1)*(1-IF(2034&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(9-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="C13" s="28">
+        <f>C12+B13</f>
+        <v/>
+      </c>
+      <c r="D13" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(9-1)*(1-IF(2034&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(9-1))-((Scenarios!D7*(1+Inputs!B33)^(9-1)*(1-IF(2034&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(9-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="E13" s="28">
+        <f>E12+D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="28">
+        <f>((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(9-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(9-1))-((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(9-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(9-1))-Inputs!B31)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="G13" s="28">
+        <f>G12+F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="28">
+        <f>Inputs!B5*(1+Inputs!B32)^9</f>
+        <v/>
+      </c>
+      <c r="I13" s="28">
+        <f>H13+C13-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="J13" s="28">
+        <f>H13+E13-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="K13" s="28">
+        <f>H13+G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B14" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(10-1)*(1-IF(2035&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(10-1))-((Scenarios!D7*(1+Inputs!B33)^(10-1)*(1-IF(2035&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(10-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="C14" s="28">
+        <f>C13+B14</f>
+        <v/>
+      </c>
+      <c r="D14" s="28">
+        <f>((Scenarios!D7*(1+Inputs!B33)^(10-1)*(1-IF(2035&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(10-1))-((Scenarios!D7*(1+Inputs!B33)^(10-1)*(1-IF(2035&gt;=2027,Inputs!B14,Inputs!B13)-Inputs!B17+Inputs!B16)-(Inputs!B18+Inputs!B19+Inputs!B20+Inputs!B21+Inputs!B22+Inputs!B23)*(1+Inputs!B34)^(10-1))-Inputs!B30)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="E14" s="28">
+        <f>E13+D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="28">
+        <f>((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(10-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(10-1))-((Inputs!B36*(52-Inputs!B37)*(1+Inputs!B33)^(10-1)*(1-Inputs!B38)-(Inputs!B39+Inputs!B40+Inputs!B41)*(1+Inputs!B34)^(10-1))-Inputs!B31)*Inputs!B29)</f>
+        <v/>
+      </c>
+      <c r="G14" s="28">
+        <f>G13+F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="28">
+        <f>Inputs!B5*(1+Inputs!B32)^10</f>
+        <v/>
+      </c>
+      <c r="I14" s="28">
+        <f>H14+C14-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="J14" s="28">
+        <f>H14+E14-Inputs!B25</f>
+        <v/>
+      </c>
+      <c r="K14" s="28">
+        <f>H14+G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Year-10 total wealth vs LTR:</t>
+        </is>
+      </c>
+      <c r="I16" s="32">
+        <f>I14-K14</f>
+        <v/>
+      </c>
+      <c r="J16" s="32">
+        <f>J14-K14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Capital gain over 10 yrs (common to all):</t>
+        </is>
+      </c>
+      <c r="H17" s="28">
+        <f>H14-Inputs!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Wealth: self = value + cumulative self-managed cash − furnishing. Growth dominates and is identical for all three.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>